--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -15886,7 +15886,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -33607,7 +33607,7 @@
           <t>D | 340呎 (1房)
 $977万
 $28,735/呎
-(26年-08月-24日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -5166,7 +5166,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -32010,7 +32010,7 @@
           <t>F | 337呎 (1房)
 $936万
 $27,763/呎
-(26年-08月-27日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -32065,7 +32065,7 @@
           <t>F | 337呎 (1房)
 $934万
 $27,703/呎
-(26年-08月-27日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -20283,34 +20283,34 @@
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
-        <v>20189000</v>
+        <v>17565000</v>
       </c>
       <c r="I298" s="5" t="n">
-        <v>34990</v>
+        <v>30442</v>
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K298" s="5" t="n">
-        <v>17564430</v>
+        <v>17565000</v>
       </c>
       <c r="L298" s="5" t="n">
-        <v>30441</v>
+        <v>30442</v>
       </c>
       <c r="M298" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N298" s="3" t="inlineStr">
@@ -22541,34 +22541,34 @@
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
-        <v>21583000</v>
+        <v>18562000</v>
       </c>
       <c r="I333" s="5" t="n">
-        <v>38336</v>
+        <v>32970</v>
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K333" s="5" t="n">
-        <v>18561380</v>
+        <v>18562000</v>
       </c>
       <c r="L333" s="5" t="n">
-        <v>32969</v>
+        <v>32970</v>
       </c>
       <c r="M333" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N333" s="3" t="inlineStr">
@@ -33131,7 +33131,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -34241,12 +34241,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
-$2019万
-$34,990/呎
-(在售)</t>
+$1756万
+$30,442/呎
+(26年-09月-20日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -34464,7 +34464,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -34474,7 +34474,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -34730,12 +34730,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
-$2158万
-$38,336/呎
-(在售)</t>
+$1856万
+$32,970/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -123,6 +123,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -209,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -274,10 +279,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -769,7 +777,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1041,7 +1049,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1243,7 +1251,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1253,12 +1261,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1268,12 +1276,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1283,7 +1291,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1663,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1665,12 +1673,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1680,12 +1688,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1695,7 +1703,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2075,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2077,12 +2085,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2092,12 +2100,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2107,7 +2115,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3311,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3313,12 +3321,12 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -3328,12 +3336,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -3343,7 +3351,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3521,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3715,7 +3723,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3725,12 +3733,12 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3740,12 +3748,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3755,7 +3763,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3933,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -4127,7 +4135,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4137,12 +4145,12 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -4152,12 +4160,12 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -4167,7 +4175,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4350,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4749,7 +4757,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4951,7 +4959,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4961,12 +4969,12 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -4976,12 +4984,12 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -4991,7 +4999,7 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5371,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -5373,12 +5381,12 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -5388,12 +5396,12 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -5403,7 +5411,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5783,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5785,12 +5793,12 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -5800,12 +5808,12 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -5815,7 +5823,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5993,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -6187,7 +6195,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -6197,12 +6205,12 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
@@ -6212,12 +6220,12 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -6227,7 +6235,7 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6405,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6809,7 +6817,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -7011,7 +7019,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -7021,12 +7029,12 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -7036,12 +7044,12 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
@@ -7051,7 +7059,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7431,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -7433,12 +7441,12 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr">
@@ -7448,12 +7456,12 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
@@ -7463,7 +7471,7 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7641,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -7835,7 +7843,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -7845,12 +7853,12 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
@@ -7860,12 +7868,12 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M106" s="3" t="inlineStr">
@@ -7875,7 +7883,7 @@
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8255,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -8257,12 +8265,12 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr">
@@ -8272,12 +8280,12 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M112" s="3" t="inlineStr">
@@ -8287,7 +8295,7 @@
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9079,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -9081,12 +9089,12 @@
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
@@ -9096,12 +9104,12 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M124" s="3" t="inlineStr">
@@ -9111,7 +9119,7 @@
       </c>
       <c r="N124" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9289,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -9483,7 +9491,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -9493,12 +9501,12 @@
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
@@ -9508,12 +9516,12 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M130" s="3" t="inlineStr">
@@ -9523,7 +9531,7 @@
       </c>
       <c r="N130" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9903,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9905,12 +9913,12 @@
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr">
@@ -9920,12 +9928,12 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M136" s="3" t="inlineStr">
@@ -9935,7 +9943,7 @@
       </c>
       <c r="N136" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10315,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -10317,12 +10325,12 @@
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J142" s="3" t="inlineStr">
@@ -10332,12 +10340,12 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M142" s="3" t="inlineStr">
@@ -10347,7 +10355,7 @@
       </c>
       <c r="N142" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10727,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -10729,12 +10737,12 @@
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J148" s="3" t="inlineStr">
@@ -10744,12 +10752,12 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M148" s="3" t="inlineStr">
@@ -10759,7 +10767,7 @@
       </c>
       <c r="N148" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11543,7 +11551,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -11553,12 +11561,12 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J160" s="3" t="inlineStr">
@@ -11568,12 +11576,12 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M160" s="3" t="inlineStr">
@@ -11583,7 +11591,7 @@
       </c>
       <c r="N160" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11955,7 +11963,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -11965,12 +11973,12 @@
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J166" s="3" t="inlineStr">
@@ -11980,12 +11988,12 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M166" s="3" t="inlineStr">
@@ -11995,7 +12003,7 @@
       </c>
       <c r="N166" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12367,7 +12375,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -12377,12 +12385,12 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J172" s="3" t="inlineStr">
@@ -12392,12 +12400,12 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
@@ -12407,7 +12415,7 @@
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12779,7 +12787,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12789,12 +12797,12 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J178" s="3" t="inlineStr">
@@ -12804,12 +12812,12 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
@@ -12819,7 +12827,7 @@
       </c>
       <c r="N178" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13409,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -13587,7 +13595,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -13840,7 +13848,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -14083,7 +14091,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -14827,7 +14835,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -16129,7 +16137,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -16315,7 +16323,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -16377,7 +16385,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -16563,7 +16571,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -16873,7 +16881,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -17369,7 +17377,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17617,7 +17625,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -17865,7 +17873,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -18113,7 +18121,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -18609,7 +18617,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -18857,7 +18865,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -19105,7 +19113,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -19353,7 +19361,7 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -19601,7 +19609,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -19849,7 +19857,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -20097,7 +20105,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -20345,7 +20353,7 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -20531,7 +20539,7 @@
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -21175,7 +21183,7 @@
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -21237,7 +21245,7 @@
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -21563,7 +21571,7 @@
       </c>
       <c r="F318" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -21827,7 +21835,7 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -21889,7 +21897,7 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -22153,7 +22161,7 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -22215,7 +22223,7 @@
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -22805,7 +22813,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -22867,7 +22875,7 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -23131,7 +23139,7 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -23783,7 +23791,7 @@
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
@@ -23845,7 +23853,7 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -24109,7 +24117,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -24435,7 +24443,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -24497,7 +24505,7 @@
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G363" s="3" t="inlineStr">
@@ -24761,7 +24769,7 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
@@ -25087,7 +25095,7 @@
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
@@ -25413,7 +25421,7 @@
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G377" s="3" t="inlineStr">
@@ -25739,7 +25747,7 @@
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
@@ -26065,7 +26073,7 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
@@ -26127,7 +26135,7 @@
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
@@ -26391,7 +26399,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -26453,7 +26461,7 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -26717,7 +26725,7 @@
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -27043,7 +27051,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -27369,7 +27377,7 @@
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
@@ -27695,7 +27703,7 @@
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -28021,7 +28029,7 @@
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G417" s="3" t="inlineStr">
@@ -28347,7 +28355,7 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
@@ -28673,7 +28681,7 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -28999,7 +29007,7 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -29325,7 +29333,7 @@
       </c>
       <c r="F437" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G437" s="3" t="inlineStr">
@@ -29651,7 +29659,7 @@
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
@@ -31307,27 +31315,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>130</t>
         </is>
       </c>
     </row>
@@ -31405,7 +31413,7 @@
           <t>F | 337呎 (1房)
 $1116万
 $33,110/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31431,12 +31439,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -31460,7 +31468,7 @@
           <t>F | 337呎 (1房)
 $1113万
 $33,033/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31486,31 +31494,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $955万
@@ -31541,31 +31549,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $942万
@@ -31620,7 +31628,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $940万
@@ -31675,7 +31683,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $936万
@@ -31706,31 +31714,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $934万
@@ -31761,12 +31769,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -31790,7 +31798,7 @@
           <t>F | 337呎 (1房)
 $1097万
 $32,552/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31816,12 +31824,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -31845,7 +31853,7 @@
           <t>F | 337呎 (1房)
 $1095万
 $32,481/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31895,12 +31903,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $940万
 $27,878/呎
-(26年-08月-31日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -31926,12 +31934,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -31955,7 +31963,7 @@
           <t>F | 337呎 (1房)
 $1090万
 $32,347/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31981,31 +31989,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $936万
@@ -32036,31 +32044,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $934万
@@ -32091,12 +32099,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -32120,7 +32128,7 @@
           <t>F | 337呎 (1房)
 $1083万
 $32,142/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -32175,7 +32183,7 @@
           <t>F | 337呎 (1房)
 $1079万
 $32,018/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -32201,12 +32209,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -32230,7 +32238,7 @@
           <t>F | 337呎 (1房)
 $1077万
 $31,953/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -32256,31 +32264,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="inlineStr">
+      <c r="G21" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $957万
@@ -32311,12 +32319,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -32340,7 +32348,7 @@
           <t>F | 337呎 (1房)
 $1072万
 $31,825/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -32366,31 +32374,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="23" t="inlineStr">
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $910万
@@ -32445,7 +32453,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $919万
@@ -32476,31 +32484,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $917万
@@ -32531,12 +32539,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -32560,7 +32568,7 @@
           <t>F | 337呎 (1房)
 $1064万
 $31,570/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -32586,31 +32594,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="G27" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $913万
@@ -32641,31 +32649,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $910万
@@ -32696,31 +32704,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="inlineStr">
+      <c r="G29" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $897万
@@ -32775,7 +32783,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $894万
@@ -32806,31 +32814,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="inlineStr">
+      <c r="G31" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $892万
@@ -32861,31 +32869,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G32" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $890万
@@ -32916,31 +32924,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="inlineStr">
+      <c r="G33" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $888万
@@ -32971,31 +32979,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="inlineStr">
+      <c r="G34" s="24" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $918万
@@ -33050,7 +33058,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G35" s="23" t="inlineStr">
+      <c r="G35" s="24" t="inlineStr">
         <is>
           <t>F | 300呎 (1房)
 $912万
@@ -33131,12 +33139,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -33193,10 +33201,10 @@
           <t>A | 577呎 (2房)
 $2221万
 $38,485/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $949万
@@ -33204,7 +33212,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1243万
@@ -33217,7 +33225,7 @@
           <t>D | 340呎 (1房)
 $1127万
 $33,144/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33227,15 +33235,15 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1904万
 $32,990/呎
-(26年-08月-31日)</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
+(26年-09月-22日)</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $992万
@@ -33243,7 +33251,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1240万
@@ -33251,7 +33259,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $956万
@@ -33271,10 +33279,10 @@
           <t>A | 577呎 (2房)
 $2206万
 $38,232/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $989万
@@ -33282,7 +33290,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1296万
@@ -33290,7 +33298,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $999万
@@ -33305,7 +33313,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1935万
@@ -33313,7 +33321,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $943万
@@ -33321,7 +33329,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1235万
@@ -33329,7 +33337,7 @@
 (26年-04月-20日)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $996万
@@ -33344,7 +33352,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1863万
@@ -33352,7 +33360,7 @@
 (26年-06月-22日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $941万
@@ -33360,7 +33368,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1232万
@@ -33368,7 +33376,7 @@
 (26年-04月-20日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $950万
@@ -33388,10 +33396,10 @@
           <t>A | 577呎 (2房)
 $2178万
 $37,754/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $954万
@@ -33399,7 +33407,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1227万
@@ -33407,7 +33415,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $946万
@@ -33422,7 +33430,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1846万
@@ -33430,7 +33438,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $935万
@@ -33438,7 +33446,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1225万
@@ -33446,7 +33454,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $941万
@@ -33461,7 +33469,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1840万
@@ -33469,7 +33477,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $933万
@@ -33477,7 +33485,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1222万
@@ -33485,7 +33493,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $939万
@@ -33500,7 +33508,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1834万
@@ -33508,7 +33516,7 @@
 (26年-04月-28日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $975万
@@ -33516,7 +33524,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1277万
@@ -33524,7 +33532,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $937万
@@ -33539,7 +33547,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1829万
@@ -33547,7 +33555,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $929万
@@ -33555,7 +33563,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1260万
@@ -33563,7 +33571,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $979万
@@ -33578,7 +33586,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1844万
@@ -33586,7 +33594,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $927万
@@ -33594,7 +33602,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1272万
@@ -33602,7 +33610,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $977万
@@ -33622,10 +33630,10 @@
           <t>A | 577呎 (2房)
 $2138万
 $37,049/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $925万
@@ -33633,7 +33641,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1212万
@@ -33646,7 +33654,7 @@
           <t>D | 340呎 (1房)
 $1095万
 $32,218/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33661,10 +33669,10 @@
           <t>A | 577呎 (2房)
 $2131万
 $36,932/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $923万
@@ -33672,7 +33680,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1209万
@@ -33685,7 +33693,7 @@
           <t>D | 340呎 (1房)
 $1093万
 $32,150/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33695,7 +33703,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1869万
@@ -33703,7 +33711,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $921万
@@ -33711,7 +33719,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1250万
@@ -33719,7 +33727,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $938万
@@ -33734,7 +33742,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1795万
@@ -33742,7 +33750,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $934万
@@ -33750,7 +33758,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1202万
@@ -33763,7 +33771,7 @@
           <t>D | 340呎 (1房)
 $1086万
 $31,956/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33773,7 +33781,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1874万
@@ -33781,7 +33789,7 @@
 (26年-08月-06日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $948万
@@ -33789,7 +33797,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1200万
@@ -33797,7 +33805,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $965万
@@ -33812,7 +33820,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1784万
@@ -33820,7 +33828,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $957万
@@ -33828,7 +33836,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1197万
@@ -33841,7 +33849,7 @@
           <t>D | 340呎 (1房)
 $1082万
 $31,829/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33851,7 +33859,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1779万
@@ -33859,7 +33867,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $955万
@@ -33867,7 +33875,7 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1195万
@@ -33880,7 +33888,7 @@
           <t>D | 340呎 (1房)
 $1080万
 $31,765/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33890,7 +33898,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1774万
@@ -33898,7 +33906,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $953万
@@ -33906,7 +33914,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1192万
@@ -33919,7 +33927,7 @@
           <t>D | 340呎 (1房)
 $1076万
 $31,638/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33937,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1831万
@@ -33937,7 +33945,7 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $909万
@@ -33945,7 +33953,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1190万
@@ -33958,7 +33966,7 @@
           <t>D | 340呎 (1房)
 $1074万
 $31,576/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33968,7 +33976,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1846万
@@ -33976,7 +33984,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $907万
@@ -33984,7 +33992,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1244万
@@ -33992,7 +34000,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $954万
@@ -34007,7 +34015,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1758万
@@ -34015,7 +34023,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $952万
@@ -34023,7 +34031,7 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1247万
@@ -34036,7 +34044,7 @@
           <t>D | 340呎 (1房)
 $1079万
 $31,735/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -34046,7 +34054,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1752万
@@ -34054,7 +34062,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $908万
@@ -34062,7 +34070,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1189万
@@ -34075,7 +34083,7 @@
           <t>D | 340呎 (1房)
 $1077万
 $31,671/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -34085,7 +34093,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1742万
@@ -34093,7 +34101,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $904万
@@ -34101,7 +34109,7 @@
 (26年-05月-14日)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1226万
@@ -34114,7 +34122,7 @@
           <t>D | 340呎 (1房)
 $1072万
 $31,544/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -34124,7 +34132,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1767万
@@ -34132,7 +34140,7 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $918万
@@ -34140,7 +34148,7 @@
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1182万
@@ -34153,7 +34161,7 @@
           <t>D | 340呎 (1房)
 $1070万
 $31,482/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -34163,7 +34171,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1732万
@@ -34171,7 +34179,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $904万
@@ -34179,7 +34187,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1218万
@@ -34192,7 +34200,7 @@
           <t>D | 340呎 (1房)
 $1068万
 $31,418/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -34202,7 +34210,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1721万
@@ -34210,7 +34218,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $897万
@@ -34218,7 +34226,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1230万
@@ -34231,7 +34239,7 @@
           <t>D | 340呎 (1房)
 $1066万
 $31,356/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -34241,7 +34249,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1756万
@@ -34249,7 +34257,7 @@
 (26年-09月-20日)</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $895万
@@ -34257,7 +34265,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1172万
@@ -34270,7 +34278,7 @@
           <t>D | 340呎 (1房)
 $1064万
 $31,294/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -34285,10 +34293,10 @@
           <t>A | 577呎 (2房)
 $2013万
 $34,884/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $893万
@@ -34296,7 +34304,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1225万
@@ -34309,7 +34317,7 @@
           <t>D | 340呎 (1房)
 $1062万
 $31,229/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -34319,7 +34327,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1706万
@@ -34327,7 +34335,7 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $933万
@@ -34335,7 +34343,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1168万
@@ -34343,7 +34351,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $901万
@@ -34358,7 +34366,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 539呎 (2房)
 招标单位
@@ -34366,7 +34374,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 301呎 (1房)
 招标单位
@@ -34374,7 +34382,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 $1250万
@@ -34382,7 +34390,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 302呎 (1房)
 招标单位
@@ -34464,12 +34472,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -34547,7 +34555,7 @@
           <t>C | 563呎 (2房)
 $2186万
 $38,831/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -34555,10 +34563,10 @@
           <t>D | 342呎 (1房)
 $1145万
 $33,485/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1145万
@@ -34594,10 +34602,10 @@
           <t>C | 563呎 (2房)
 $2179万
 $38,705/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>D | 342呎 (1房)
 $989万
@@ -34605,7 +34613,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1183万
@@ -34641,7 +34649,7 @@
           <t>C | 563呎 (2房)
 $2152万
 $38,233/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -34649,10 +34657,10 @@
           <t>D | 342呎 (1房)
 $1140万
 $33,342/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1140万
@@ -34688,7 +34696,7 @@
           <t>C | 563呎 (2房)
 $2146万
 $38,112/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -34696,10 +34704,10 @@
           <t>D | 342呎 (1房)
 $1138万
 $33,272/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1138万
@@ -34730,7 +34738,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1856万
@@ -34738,7 +34746,7 @@
 (26年-09月-18日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>D | 342呎 (1房)
 $965万
@@ -34746,7 +34754,7 @@
 (26年-07月-22日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1135万
@@ -34782,7 +34790,7 @@
           <t>C | 563呎 (2房)
 $2145万
 $38,096/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -34790,10 +34798,10 @@
           <t>D | 342呎 (1房)
 $1131万
 $33,064/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1170万
@@ -34824,7 +34832,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1833万
@@ -34837,10 +34845,10 @@
           <t>D | 342呎 (1房)
 $1125万
 $32,895/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1125万
@@ -34871,7 +34879,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1796万
@@ -34879,7 +34887,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>D | 342呎 (1房)
 $960万
@@ -34887,7 +34895,7 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1123万
@@ -34923,7 +34931,7 @@
           <t>C | 563呎 (2房)
 $2125万
 $37,737/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -34931,10 +34939,10 @@
           <t>D | 342呎 (1房)
 $1120万
 $32,757/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1120万
@@ -34965,7 +34973,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1800万
@@ -34978,10 +34986,10 @@
           <t>D | 342呎 (1房)
 $1118万
 $32,690/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1157万
@@ -35017,7 +35025,7 @@
           <t>C | 563呎 (2房)
 $2111万
 $37,501/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -35025,10 +35033,10 @@
           <t>D | 342呎 (1房)
 $1116万
 $32,620/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1116万
@@ -35059,7 +35067,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1789万
@@ -35072,10 +35080,10 @@
           <t>D | 342呎 (1房)
 $1113万
 $32,553/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1152万
@@ -35106,7 +35114,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1768万
@@ -35119,10 +35127,10 @@
           <t>D | 342呎 (1房)
 $1111万
 $32,485/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1111万
@@ -35153,7 +35161,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1845万
@@ -35166,10 +35174,10 @@
           <t>D | 342呎 (1房)
 $1109万
 $32,415/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1161万
@@ -35200,7 +35208,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1767万
@@ -35213,10 +35221,10 @@
           <t>D | 342呎 (1房)
 $1104万
 $32,287/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1156万
@@ -35252,7 +35260,7 @@
           <t>C | 563呎 (2房)
 $2073万
 $36,817/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -35260,10 +35268,10 @@
           <t>D | 342呎 (1房)
 $1102万
 $32,219/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1154万
@@ -35299,7 +35307,7 @@
           <t>C | 563呎 (2房)
 $2066万
 $36,705/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -35307,10 +35315,10 @@
           <t>D | 342呎 (1房)
 $1100万
 $32,158/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1100万
@@ -35341,7 +35349,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1736万
@@ -35354,10 +35362,10 @@
           <t>D | 342呎 (1房)
 $1098万
 $32,096/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1098万
@@ -35388,7 +35396,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1731万
@@ -35401,10 +35409,10 @@
           <t>D | 342呎 (1房)
 $1093万
 $31,962/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1093万
@@ -35435,7 +35443,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1725万
@@ -35448,10 +35456,10 @@
           <t>D | 342呎 (1房)
 $1091万
 $31,904/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1091万
@@ -35482,7 +35490,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1736万
@@ -35495,10 +35503,10 @@
           <t>D | 342呎 (1房)
 $1089万
 $31,839/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1089万
@@ -35529,7 +35537,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1731万
@@ -35542,10 +35550,10 @@
           <t>D | 342呎 (1房)
 $1087万
 $31,778/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1087万
@@ -35576,7 +35584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1790万
@@ -35589,10 +35597,10 @@
           <t>D | 342呎 (1房)
 $1084万
 $31,711/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1084万
@@ -35623,7 +35631,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1700万
@@ -35636,10 +35644,10 @@
           <t>D | 342呎 (1房)
 $1080万
 $31,585/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1080万
@@ -35670,7 +35678,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1695万
@@ -35683,10 +35691,10 @@
           <t>D | 342呎 (1房)
 $1078万
 $31,523/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1129万
@@ -35717,7 +35725,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1705万
@@ -35730,10 +35738,10 @@
           <t>D | 342呎 (1房)
 $1076万
 $31,462/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1076万
@@ -35764,7 +35772,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1680万
@@ -35777,10 +35785,10 @@
           <t>D | 342呎 (1房)
 $1074万
 $31,395/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1074万
@@ -35811,7 +35819,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1674万
@@ -35827,7 +35835,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F32" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1078万
@@ -35858,7 +35866,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1669万
@@ -35874,7 +35882,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1107万
@@ -35905,7 +35913,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1679万
@@ -35921,7 +35929,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F34" s="24" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1067万
@@ -35952,7 +35960,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 525呎 (2房)
 招标单位
@@ -35960,7 +35968,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>D | 304呎 (1房)
 $1021万
@@ -35968,7 +35976,7 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>E | 363呎 (2房)
 招标单位

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -123,11 +123,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -214,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -279,13 +274,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -777,7 +769,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1049,7 +1041,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -3521,7 +3513,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3933,7 +3925,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -4757,7 +4749,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -5993,7 +5985,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -6405,7 +6397,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6817,7 +6809,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -7641,7 +7633,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -9289,7 +9281,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -13409,7 +13401,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -13595,7 +13587,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -14091,7 +14083,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -14835,7 +14827,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -16137,7 +16129,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -16323,7 +16315,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -16385,7 +16377,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -16571,7 +16563,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -16881,7 +16873,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -17377,7 +17369,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17625,7 +17617,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -17873,7 +17865,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -18121,7 +18113,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -18617,7 +18609,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -18865,7 +18857,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -19113,7 +19105,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -19361,7 +19353,7 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -19609,7 +19601,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -19857,7 +19849,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -20105,7 +20097,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -20353,7 +20345,7 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -20539,7 +20531,7 @@
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -21183,7 +21175,7 @@
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -21245,7 +21237,7 @@
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -21571,7 +21563,7 @@
       </c>
       <c r="F318" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -21835,7 +21827,7 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -21897,7 +21889,7 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -22161,7 +22153,7 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -22223,7 +22215,7 @@
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -22813,7 +22805,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -22875,7 +22867,7 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -23139,7 +23131,7 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -23791,7 +23783,7 @@
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
@@ -23853,7 +23845,7 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -24117,7 +24109,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -24443,7 +24435,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -24505,7 +24497,7 @@
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G363" s="3" t="inlineStr">
@@ -24769,7 +24761,7 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
@@ -25095,7 +25087,7 @@
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
@@ -25421,7 +25413,7 @@
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G377" s="3" t="inlineStr">
@@ -25747,7 +25739,7 @@
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
@@ -26073,7 +26065,7 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
@@ -26135,7 +26127,7 @@
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
@@ -26399,7 +26391,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -26461,7 +26453,7 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -26725,7 +26717,7 @@
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -27051,7 +27043,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -27377,7 +27369,7 @@
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
@@ -27703,7 +27695,7 @@
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -28029,7 +28021,7 @@
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G417" s="3" t="inlineStr">
@@ -28355,7 +28347,7 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
@@ -28681,7 +28673,7 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -29007,7 +28999,7 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -29333,7 +29325,7 @@
       </c>
       <c r="F437" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G437" s="3" t="inlineStr">
@@ -29659,7 +29651,7 @@
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
@@ -31315,12 +31307,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -31413,7 +31405,7 @@
           <t>F | 337呎 (1房)
 $1116万
 $33,110/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31439,7 +31431,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -31468,7 +31460,7 @@
           <t>F | 337呎 (1房)
 $1113万
 $33,033/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31494,7 +31486,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -31518,7 +31510,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $955万
@@ -31549,7 +31541,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -31573,7 +31565,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $942万
@@ -31628,7 +31620,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $940万
@@ -31683,7 +31675,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $936万
@@ -31714,7 +31706,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -31738,7 +31730,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $934万
@@ -31769,7 +31761,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -31798,7 +31790,7 @@
           <t>F | 337呎 (1房)
 $1097万
 $32,552/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31824,7 +31816,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -31853,7 +31845,7 @@
           <t>F | 337呎 (1房)
 $1095万
 $32,481/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31903,7 +31895,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $940万
@@ -31934,7 +31926,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -31963,7 +31955,7 @@
           <t>F | 337呎 (1房)
 $1090万
 $32,347/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31989,7 +31981,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32013,7 +32005,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $936万
@@ -32044,7 +32036,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32068,7 +32060,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $934万
@@ -32099,7 +32091,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32128,7 +32120,7 @@
           <t>F | 337呎 (1房)
 $1083万
 $32,142/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -32183,7 +32175,7 @@
           <t>F | 337呎 (1房)
 $1079万
 $32,018/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -32209,7 +32201,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32238,7 +32230,7 @@
           <t>F | 337呎 (1房)
 $1077万
 $31,953/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -32264,7 +32256,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32288,7 +32280,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G21" s="24" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $957万
@@ -32319,7 +32311,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32348,7 +32340,7 @@
           <t>F | 337呎 (1房)
 $1072万
 $31,825/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32366,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32398,7 +32390,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G23" s="24" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $910万
@@ -32453,7 +32445,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G24" s="24" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $919万
@@ -32484,7 +32476,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32508,7 +32500,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G25" s="24" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $917万
@@ -32539,7 +32531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32568,7 +32560,7 @@
           <t>F | 337呎 (1房)
 $1064万
 $31,570/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -32594,7 +32586,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32618,7 +32610,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G27" s="24" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $913万
@@ -32649,7 +32641,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32673,7 +32665,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="24" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $910万
@@ -32704,7 +32696,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32728,7 +32720,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G29" s="24" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $897万
@@ -32783,7 +32775,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G30" s="24" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $894万
@@ -32814,7 +32806,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32838,7 +32830,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G31" s="24" t="inlineStr">
+      <c r="G31" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $892万
@@ -32869,7 +32861,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32893,7 +32885,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G32" s="24" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $890万
@@ -32924,7 +32916,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -32948,7 +32940,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G33" s="24" t="inlineStr">
+      <c r="G33" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $888万
@@ -32979,7 +32971,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
 招标单位
@@ -33003,7 +32995,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G34" s="24" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $918万
@@ -33058,7 +33050,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G35" s="24" t="inlineStr">
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>F | 300呎 (1房)
 $912万
@@ -33139,12 +33131,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -33201,10 +33193,10 @@
           <t>A | 577呎 (2房)
 $2221万
 $38,485/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $949万
@@ -33212,7 +33204,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1243万
@@ -33225,7 +33217,7 @@
           <t>D | 340呎 (1房)
 $1127万
 $33,144/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33227,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1904万
@@ -33243,7 +33235,7 @@
 (26年-09月-22日)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $992万
@@ -33251,7 +33243,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1240万
@@ -33259,7 +33251,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $956万
@@ -33279,10 +33271,10 @@
           <t>A | 577呎 (2房)
 $2206万
 $38,232/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $989万
@@ -33290,7 +33282,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1296万
@@ -33298,7 +33290,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $999万
@@ -33313,7 +33305,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1935万
@@ -33321,7 +33313,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $943万
@@ -33329,7 +33321,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1235万
@@ -33337,7 +33329,7 @@
 (26年-04月-20日)</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $996万
@@ -33352,7 +33344,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1863万
@@ -33360,7 +33352,7 @@
 (26年-06月-22日)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $941万
@@ -33368,7 +33360,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1232万
@@ -33376,7 +33368,7 @@
 (26年-04月-20日)</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $950万
@@ -33396,10 +33388,10 @@
           <t>A | 577呎 (2房)
 $2178万
 $37,754/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $954万
@@ -33407,7 +33399,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1227万
@@ -33415,7 +33407,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $946万
@@ -33430,7 +33422,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1846万
@@ -33438,7 +33430,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $935万
@@ -33446,7 +33438,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1225万
@@ -33454,7 +33446,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $941万
@@ -33469,7 +33461,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1840万
@@ -33477,7 +33469,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $933万
@@ -33485,7 +33477,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1222万
@@ -33493,7 +33485,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $939万
@@ -33508,7 +33500,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1834万
@@ -33516,7 +33508,7 @@
 (26年-04月-28日)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $975万
@@ -33524,7 +33516,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1277万
@@ -33532,7 +33524,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $937万
@@ -33547,7 +33539,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1829万
@@ -33555,7 +33547,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $929万
@@ -33563,7 +33555,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1260万
@@ -33571,7 +33563,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $979万
@@ -33586,7 +33578,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1844万
@@ -33594,7 +33586,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $927万
@@ -33602,7 +33594,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1272万
@@ -33610,7 +33602,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $977万
@@ -33630,10 +33622,10 @@
           <t>A | 577呎 (2房)
 $2138万
 $37,049/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $925万
@@ -33641,7 +33633,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1212万
@@ -33654,7 +33646,7 @@
           <t>D | 340呎 (1房)
 $1095万
 $32,218/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -33669,10 +33661,10 @@
           <t>A | 577呎 (2房)
 $2131万
 $36,932/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $923万
@@ -33680,7 +33672,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1209万
@@ -33693,7 +33685,7 @@
           <t>D | 340呎 (1房)
 $1093万
 $32,150/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -33703,7 +33695,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1869万
@@ -33711,7 +33703,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $921万
@@ -33719,7 +33711,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1250万
@@ -33727,7 +33719,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $938万
@@ -33742,7 +33734,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1795万
@@ -33750,7 +33742,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $934万
@@ -33758,7 +33750,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1202万
@@ -33771,7 +33763,7 @@
           <t>D | 340呎 (1房)
 $1086万
 $31,956/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -33781,7 +33773,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1874万
@@ -33789,7 +33781,7 @@
 (26年-08月-06日)</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $948万
@@ -33797,7 +33789,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1200万
@@ -33805,7 +33797,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $965万
@@ -33820,7 +33812,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1784万
@@ -33828,7 +33820,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $957万
@@ -33836,7 +33828,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1197万
@@ -33849,7 +33841,7 @@
           <t>D | 340呎 (1房)
 $1082万
 $31,829/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -33859,7 +33851,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1779万
@@ -33867,7 +33859,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $955万
@@ -33875,7 +33867,7 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1195万
@@ -33888,7 +33880,7 @@
           <t>D | 340呎 (1房)
 $1080万
 $31,765/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -33898,7 +33890,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1774万
@@ -33906,7 +33898,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $953万
@@ -33914,7 +33906,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1192万
@@ -33927,7 +33919,7 @@
           <t>D | 340呎 (1房)
 $1076万
 $31,638/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -33937,7 +33929,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1831万
@@ -33945,7 +33937,7 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $909万
@@ -33953,7 +33945,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1190万
@@ -33966,7 +33958,7 @@
           <t>D | 340呎 (1房)
 $1074万
 $31,576/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -33976,7 +33968,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1846万
@@ -33984,7 +33976,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $907万
@@ -33992,7 +33984,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1244万
@@ -34000,7 +33992,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $954万
@@ -34015,7 +34007,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1758万
@@ -34023,7 +34015,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $952万
@@ -34031,7 +34023,7 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1247万
@@ -34044,7 +34036,7 @@
           <t>D | 340呎 (1房)
 $1079万
 $31,735/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -34054,7 +34046,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1752万
@@ -34062,7 +34054,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $908万
@@ -34070,7 +34062,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1189万
@@ -34083,7 +34075,7 @@
           <t>D | 340呎 (1房)
 $1077万
 $31,671/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -34093,7 +34085,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1742万
@@ -34101,7 +34093,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $904万
@@ -34109,7 +34101,7 @@
 (26年-05月-14日)</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1226万
@@ -34122,7 +34114,7 @@
           <t>D | 340呎 (1房)
 $1072万
 $31,544/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -34132,7 +34124,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1767万
@@ -34140,7 +34132,7 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $918万
@@ -34148,7 +34140,7 @@
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1182万
@@ -34161,7 +34153,7 @@
           <t>D | 340呎 (1房)
 $1070万
 $31,482/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -34171,7 +34163,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1732万
@@ -34179,7 +34171,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $904万
@@ -34187,7 +34179,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1218万
@@ -34200,7 +34192,7 @@
           <t>D | 340呎 (1房)
 $1068万
 $31,418/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -34210,7 +34202,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1721万
@@ -34218,7 +34210,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $897万
@@ -34226,7 +34218,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1230万
@@ -34239,7 +34231,7 @@
           <t>D | 340呎 (1房)
 $1066万
 $31,356/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -34249,7 +34241,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1756万
@@ -34257,7 +34249,7 @@
 (26年-09月-20日)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $895万
@@ -34265,7 +34257,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1172万
@@ -34278,7 +34270,7 @@
           <t>D | 340呎 (1房)
 $1064万
 $31,294/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -34293,10 +34285,10 @@
           <t>A | 577呎 (2房)
 $2013万
 $34,884/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $893万
@@ -34304,7 +34296,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1225万
@@ -34317,7 +34309,7 @@
           <t>D | 340呎 (1房)
 $1062万
 $31,229/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -34327,7 +34319,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
 $1706万
@@ -34335,7 +34327,7 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 337呎 (1房)
 $933万
@@ -34343,7 +34335,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 440呎 (2房)
 $1168万
@@ -34351,7 +34343,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $901万
@@ -34366,7 +34358,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 539呎 (2房)
 招标单位
@@ -34374,7 +34366,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 301呎 (1房)
 招标单位
@@ -34382,7 +34374,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 $1250万
@@ -34390,7 +34382,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 302呎 (1房)
 招标单位
@@ -34472,12 +34464,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -34555,7 +34547,7 @@
           <t>C | 563呎 (2房)
 $2186万
 $38,831/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -34563,10 +34555,10 @@
           <t>D | 342呎 (1房)
 $1145万
 $33,485/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F5" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1145万
@@ -34602,10 +34594,10 @@
           <t>C | 563呎 (2房)
 $2179万
 $38,705/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E6" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>D | 342呎 (1房)
 $989万
@@ -34613,7 +34605,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1183万
@@ -34649,7 +34641,7 @@
           <t>C | 563呎 (2房)
 $2152万
 $38,233/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -34657,10 +34649,10 @@
           <t>D | 342呎 (1房)
 $1140万
 $33,342/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1140万
@@ -34696,7 +34688,7 @@
           <t>C | 563呎 (2房)
 $2146万
 $38,112/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -34704,10 +34696,10 @@
           <t>D | 342呎 (1房)
 $1138万
 $33,272/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1138万
@@ -34738,7 +34730,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1856万
@@ -34746,7 +34738,7 @@
 (26年-09月-18日)</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 342呎 (1房)
 $965万
@@ -34754,7 +34746,7 @@
 (26年-07月-22日)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1135万
@@ -34790,7 +34782,7 @@
           <t>C | 563呎 (2房)
 $2145万
 $38,096/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -34798,10 +34790,10 @@
           <t>D | 342呎 (1房)
 $1131万
 $33,064/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1170万
@@ -34832,7 +34824,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1833万
@@ -34845,10 +34837,10 @@
           <t>D | 342呎 (1房)
 $1125万
 $32,895/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1125万
@@ -34879,7 +34871,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1796万
@@ -34887,7 +34879,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 342呎 (1房)
 $960万
@@ -34895,7 +34887,7 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1123万
@@ -34931,7 +34923,7 @@
           <t>C | 563呎 (2房)
 $2125万
 $37,737/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -34939,10 +34931,10 @@
           <t>D | 342呎 (1房)
 $1120万
 $32,757/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1120万
@@ -34973,7 +34965,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1800万
@@ -34986,10 +34978,10 @@
           <t>D | 342呎 (1房)
 $1118万
 $32,690/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1157万
@@ -35025,7 +35017,7 @@
           <t>C | 563呎 (2房)
 $2111万
 $37,501/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -35033,10 +35025,10 @@
           <t>D | 342呎 (1房)
 $1116万
 $32,620/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1116万
@@ -35067,7 +35059,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1789万
@@ -35080,10 +35072,10 @@
           <t>D | 342呎 (1房)
 $1113万
 $32,553/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1152万
@@ -35114,7 +35106,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1768万
@@ -35127,10 +35119,10 @@
           <t>D | 342呎 (1房)
 $1111万
 $32,485/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1111万
@@ -35161,7 +35153,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1845万
@@ -35174,10 +35166,10 @@
           <t>D | 342呎 (1房)
 $1109万
 $32,415/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1161万
@@ -35208,7 +35200,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1767万
@@ -35221,10 +35213,10 @@
           <t>D | 342呎 (1房)
 $1104万
 $32,287/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1156万
@@ -35260,7 +35252,7 @@
           <t>C | 563呎 (2房)
 $2073万
 $36,817/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -35268,10 +35260,10 @@
           <t>D | 342呎 (1房)
 $1102万
 $32,219/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1154万
@@ -35307,7 +35299,7 @@
           <t>C | 563呎 (2房)
 $2066万
 $36,705/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -35315,10 +35307,10 @@
           <t>D | 342呎 (1房)
 $1100万
 $32,158/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1100万
@@ -35349,7 +35341,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1736万
@@ -35362,10 +35354,10 @@
           <t>D | 342呎 (1房)
 $1098万
 $32,096/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1098万
@@ -35396,7 +35388,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1731万
@@ -35409,10 +35401,10 @@
           <t>D | 342呎 (1房)
 $1093万
 $31,962/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1093万
@@ -35443,7 +35435,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1725万
@@ -35456,10 +35448,10 @@
           <t>D | 342呎 (1房)
 $1091万
 $31,904/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1091万
@@ -35490,7 +35482,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1736万
@@ -35503,10 +35495,10 @@
           <t>D | 342呎 (1房)
 $1089万
 $31,839/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1089万
@@ -35537,7 +35529,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1731万
@@ -35550,10 +35542,10 @@
           <t>D | 342呎 (1房)
 $1087万
 $31,778/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1087万
@@ -35584,7 +35576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1790万
@@ -35597,10 +35589,10 @@
           <t>D | 342呎 (1房)
 $1084万
 $31,711/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1084万
@@ -35631,7 +35623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1700万
@@ -35644,10 +35636,10 @@
           <t>D | 342呎 (1房)
 $1080万
 $31,585/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F28" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1080万
@@ -35678,7 +35670,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1695万
@@ -35691,10 +35683,10 @@
           <t>D | 342呎 (1房)
 $1078万
 $31,523/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F29" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1129万
@@ -35725,7 +35717,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1705万
@@ -35738,10 +35730,10 @@
           <t>D | 342呎 (1房)
 $1076万
 $31,462/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1076万
@@ -35772,7 +35764,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1680万
@@ -35785,10 +35777,10 @@
           <t>D | 342呎 (1房)
 $1074万
 $31,395/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F31" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1074万
@@ -35819,7 +35811,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1674万
@@ -35835,7 +35827,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F32" s="24" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1078万
@@ -35866,7 +35858,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1669万
@@ -35882,7 +35874,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F33" s="24" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1107万
@@ -35913,7 +35905,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
 $1679万
@@ -35929,7 +35921,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="24" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $1067万
@@ -35960,7 +35952,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 525呎 (2房)
 招标单位
@@ -35968,7 +35960,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 304呎 (1房)
 $1021万
@@ -35976,7 +35968,7 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>E | 363呎 (2房)
 招标单位

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -2067,38 +2067,30 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>28055000</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>33801</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K22" s="5" t="n">
+        <v>28055000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>33801</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2107,7 +2099,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -11543,38 +11535,30 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>25937500</v>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>31250</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L160" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K160" s="5" t="n">
+        <v>25937500</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>31250</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
@@ -11583,7 +11567,7 @@
       </c>
       <c r="N160" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -31307,7 +31291,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31317,7 +31301,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31541,12 +31525,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
-招标单位
--
-(在售)</t>
+$2806万
+$33,801/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -32806,12 +32790,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 830呎 (3房)
-招标单位
--
-(在售)</t>
+$2594万
+$31,250/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -22530,7 +22530,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -34719,7 +34719,7 @@
           <t>C | 563呎 (2房)
 $1856万
 $32,970/呎
-(26年-09月-18日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -20272,7 +20272,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -26111,34 +26111,34 @@
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
-        <v>20728000</v>
+        <v>17827000</v>
       </c>
       <c r="I388" s="5" t="n">
-        <v>36817</v>
+        <v>31664</v>
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K388" s="5" t="n">
-        <v>17826080</v>
+        <v>17827000</v>
       </c>
       <c r="L388" s="5" t="n">
-        <v>31663</v>
+        <v>31664</v>
       </c>
       <c r="M388" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N388" s="3" t="inlineStr">
@@ -31530,7 +31530,7 @@
           <t>C | 830呎 (3房)
 $2806万
 $33,801/呎
-(26年-09月-29日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -34230,7 +34230,7 @@
           <t>A | 577呎 (2房)
 $1756万
 $30,442/呎
-(26年-09月-20日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -34448,7 +34448,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -34458,7 +34458,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35231,12 +35231,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
-$2073万
-$36,817/呎
-(在售)</t>
+$1783万
+$31,664/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -11540,7 +11540,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -26437,34 +26437,34 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
-        <v>20665000</v>
+        <v>17772000</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>36705</v>
+        <v>31567</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K393" s="5" t="n">
-        <v>17771900</v>
+        <v>17772000</v>
       </c>
       <c r="L393" s="5" t="n">
-        <v>31566</v>
+        <v>31567</v>
       </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N393" s="3" t="inlineStr">
@@ -28657,34 +28657,34 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
-        <v>10802000</v>
+        <v>9290000</v>
       </c>
       <c r="I427" s="5" t="n">
-        <v>31585</v>
+        <v>27164</v>
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K427" s="5" t="n">
-        <v>9289720</v>
+        <v>9290000</v>
       </c>
       <c r="L427" s="5" t="n">
-        <v>27163</v>
+        <v>27164</v>
       </c>
       <c r="M427" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N427" s="3" t="inlineStr">
@@ -32795,7 +32795,7 @@
           <t>C | 830呎 (3房)
 $2594万
 $31,250/呎
-(26年-09月-29日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -34448,7 +34448,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -34458,7 +34458,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35236,7 +35236,7 @@
           <t>C | 563呎 (2房)
 $1783万
 $31,664/呎
-(26年-10月-09日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -35278,12 +35278,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
-$2066万
-$36,705/呎
-(在售)</t>
+$1777万
+$31,567/呎
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -35615,12 +35615,12 @@
 (26年-05月-15日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 342呎 (1房)
-$1080万
-$31,585/呎
-(在售)</t>
+$929万
+$27,164/呎
+(26年-10月-24日)</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
